--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/29.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/29.xlsx
@@ -426,13 +426,13 @@
         <v>-11.01415183679891</v>
       </c>
       <c r="E2">
-        <v>-12.42331351444828</v>
+        <v>-12.97278496511698</v>
       </c>
       <c r="F2">
-        <v>-2.520143125151847</v>
+        <v>-1.204303871724707</v>
       </c>
       <c r="G2">
-        <v>-9.272938522533106</v>
+        <v>-9.104862125504308</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.15527263255046</v>
       </c>
       <c r="E3">
-        <v>-13.45374966099764</v>
+        <v>-14.33520806964266</v>
       </c>
       <c r="F3">
-        <v>-2.663577426048789</v>
+        <v>-1.280209661945434</v>
       </c>
       <c r="G3">
-        <v>-9.052005955424304</v>
+        <v>-8.916872797056794</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.33723315001211</v>
       </c>
       <c r="E4">
-        <v>-13.94611252595561</v>
+        <v>-14.69061176671265</v>
       </c>
       <c r="F4">
-        <v>-2.427330356239982</v>
+        <v>-1.176809529258389</v>
       </c>
       <c r="G4">
-        <v>-9.261474103330611</v>
+        <v>-9.491947662683593</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.49828105544154</v>
       </c>
       <c r="E5">
-        <v>-15.64545862512597</v>
+        <v>-15.62222755346662</v>
       </c>
       <c r="F5">
-        <v>-2.819344460838611</v>
+        <v>-1.241500881580016</v>
       </c>
       <c r="G5">
-        <v>-8.74787275782254</v>
+        <v>-8.944307287940735</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.62509566861022</v>
       </c>
       <c r="E6">
-        <v>-15.95811352756355</v>
+        <v>-16.42648906570289</v>
       </c>
       <c r="F6">
-        <v>-2.650886009070498</v>
+        <v>-1.356229766867748</v>
       </c>
       <c r="G6">
-        <v>-8.271700440181469</v>
+        <v>-9.403582581149365</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.66733334975072</v>
       </c>
       <c r="E7">
-        <v>-15.54690091682304</v>
+        <v>-16.84650050144031</v>
       </c>
       <c r="F7">
-        <v>-2.631282694483248</v>
+        <v>-1.059339576234794</v>
       </c>
       <c r="G7">
-        <v>-8.058047762713525</v>
+        <v>-8.659487813015078</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.6098182293021</v>
       </c>
       <c r="E8">
-        <v>-16.94235923923467</v>
+        <v>-17.81341574308407</v>
       </c>
       <c r="F8">
-        <v>-2.715781968140617</v>
+        <v>-1.247267147070904</v>
       </c>
       <c r="G8">
-        <v>-7.659196546687671</v>
+        <v>-8.397739529952601</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.41285514509911</v>
       </c>
       <c r="E9">
-        <v>-17.3346247147271</v>
+        <v>-17.51743921041675</v>
       </c>
       <c r="F9">
-        <v>-2.767200389567188</v>
+        <v>-0.9394971789695811</v>
       </c>
       <c r="G9">
-        <v>-7.987129256171256</v>
+        <v>-8.505911605448286</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.07836877676568</v>
       </c>
       <c r="E10">
-        <v>-18.20400115471965</v>
+        <v>-18.60386540959694</v>
       </c>
       <c r="F10">
-        <v>-2.625818783094382</v>
+        <v>-1.535586220187091</v>
       </c>
       <c r="G10">
-        <v>-7.557393960809542</v>
+        <v>-8.42854084564998</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.59582388508367</v>
       </c>
       <c r="E11">
-        <v>-18.61977846725989</v>
+        <v>-19.72782812982672</v>
       </c>
       <c r="F11">
-        <v>-2.631535346541102</v>
+        <v>-0.8889957602579092</v>
       </c>
       <c r="G11">
-        <v>-6.715995638184995</v>
+        <v>-7.47831827005851</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.00226785353454</v>
       </c>
       <c r="E12">
-        <v>-20.52382517699898</v>
+        <v>-20.59954579088124</v>
       </c>
       <c r="F12">
-        <v>-2.291617267904533</v>
+        <v>-1.115916241478597</v>
       </c>
       <c r="G12">
-        <v>-6.64484208290944</v>
+        <v>-6.745568741487305</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.32257784968988</v>
       </c>
       <c r="E13">
-        <v>-20.76003943818708</v>
+        <v>-21.00216335795519</v>
       </c>
       <c r="F13">
-        <v>-1.974751825720471</v>
+        <v>-1.000607499008906</v>
       </c>
       <c r="G13">
-        <v>-6.016060236999045</v>
+        <v>-5.783047489217442</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.62346886074026</v>
       </c>
       <c r="E14">
-        <v>-20.54329308675796</v>
+        <v>-21.82004199153252</v>
       </c>
       <c r="F14">
-        <v>-2.469133917222258</v>
+        <v>-0.4658847433581861</v>
       </c>
       <c r="G14">
-        <v>-6.151650250650975</v>
+        <v>-5.815295513315483</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.948797695368238</v>
       </c>
       <c r="E15">
-        <v>-23.25796381471408</v>
+        <v>-22.54244227913213</v>
       </c>
       <c r="F15">
-        <v>-1.731770128926904</v>
+        <v>-0.2869093390441305</v>
       </c>
       <c r="G15">
-        <v>-5.407469408332665</v>
+        <v>-5.649791410170699</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.371933540001812</v>
       </c>
       <c r="E16">
-        <v>-23.68622160161947</v>
+        <v>-23.51175308352595</v>
       </c>
       <c r="F16">
-        <v>-1.74276753456647</v>
+        <v>-0.1955503549241786</v>
       </c>
       <c r="G16">
-        <v>-4.27685189576077</v>
+        <v>-5.123358390152412</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.930039558567226</v>
       </c>
       <c r="E17">
-        <v>-23.60743068236001</v>
+        <v>-24.6459727973831</v>
       </c>
       <c r="F17">
-        <v>-1.273338354339212</v>
+        <v>0.2273452864508166</v>
       </c>
       <c r="G17">
-        <v>-4.484555522894644</v>
+        <v>-4.802232162297568</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.676628898974442</v>
       </c>
       <c r="E18">
-        <v>-23.91444763465804</v>
+        <v>-25.25375740784857</v>
       </c>
       <c r="F18">
-        <v>-0.8422551295549471</v>
+        <v>0.3400065667011605</v>
       </c>
       <c r="G18">
-        <v>-4.092000964484485</v>
+        <v>-4.688044825557026</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.616853821995338</v>
       </c>
       <c r="E19">
-        <v>-25.5588271163233</v>
+        <v>-26.03636375738015</v>
       </c>
       <c r="F19">
-        <v>-0.5161931524650056</v>
+        <v>0.5335985138376134</v>
       </c>
       <c r="G19">
-        <v>-4.06612905109508</v>
+        <v>-3.799802283551792</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.763350348195662</v>
       </c>
       <c r="E20">
-        <v>-25.99457499923737</v>
+        <v>-26.60068860279401</v>
       </c>
       <c r="F20">
-        <v>-0.604476408418363</v>
+        <v>0.8878183556835155</v>
       </c>
       <c r="G20">
-        <v>-3.902727144367733</v>
+        <v>-4.198388655934504</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.080231159648448</v>
       </c>
       <c r="E21">
-        <v>-26.84188871386456</v>
+        <v>-27.17338659664805</v>
       </c>
       <c r="F21">
-        <v>-0.3607790021887765</v>
+        <v>1.153273660115034</v>
       </c>
       <c r="G21">
-        <v>-4.062381513544626</v>
+        <v>-3.870459256996457</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.542491211821548</v>
       </c>
       <c r="E22">
-        <v>-27.16408511103629</v>
+        <v>-27.34841211704451</v>
       </c>
       <c r="F22">
-        <v>0.04352890303480067</v>
+        <v>1.180690964412892</v>
       </c>
       <c r="G22">
-        <v>-4.04014457915734</v>
+        <v>-3.733353013487541</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.089687345550834</v>
       </c>
       <c r="E23">
-        <v>-28.29912900716284</v>
+        <v>-28.43929886312226</v>
       </c>
       <c r="F23">
-        <v>0.05690040965079029</v>
+        <v>1.31016644620526</v>
       </c>
       <c r="G23">
-        <v>-4.060130342577921</v>
+        <v>-4.029176741785736</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.680183506237451</v>
       </c>
       <c r="E24">
-        <v>-27.92938363291056</v>
+        <v>-28.86082733765225</v>
       </c>
       <c r="F24">
-        <v>0.3041225191792887</v>
+        <v>1.491819133965164</v>
       </c>
       <c r="G24">
-        <v>-4.508580151873136</v>
+        <v>-4.098254585008168</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.250362613971248</v>
       </c>
       <c r="E25">
-        <v>-28.27730629091987</v>
+        <v>-28.42747954596224</v>
       </c>
       <c r="F25">
-        <v>0.211523469057346</v>
+        <v>1.034553700680614</v>
       </c>
       <c r="G25">
-        <v>-4.204192042264846</v>
+        <v>-3.523371731022648</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.760990315917246</v>
       </c>
       <c r="E26">
-        <v>-27.78497512527996</v>
+        <v>-28.69009028214105</v>
       </c>
       <c r="F26">
-        <v>-0.3288818869765787</v>
+        <v>1.169450018756903</v>
       </c>
       <c r="G26">
-        <v>-4.40058684583657</v>
+        <v>-3.244769460619742</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.16392418183799</v>
       </c>
       <c r="E27">
-        <v>-28.70854381372231</v>
+        <v>-29.27452608062297</v>
       </c>
       <c r="F27">
-        <v>0.1588583546895618</v>
+        <v>1.110079270263457</v>
       </c>
       <c r="G27">
-        <v>-4.231917861156242</v>
+        <v>-4.022701314710921</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.43875029167778</v>
       </c>
       <c r="E28">
-        <v>-28.62818151398219</v>
+        <v>-28.57485873254187</v>
       </c>
       <c r="F28">
-        <v>0.2677861830554884</v>
+        <v>1.359537143412111</v>
       </c>
       <c r="G28">
-        <v>-4.709619650836457</v>
+        <v>-4.117773561507711</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.56116557716306</v>
       </c>
       <c r="E29">
-        <v>-27.64905750641374</v>
+        <v>-28.89479089270977</v>
       </c>
       <c r="F29">
-        <v>0.09034077333440353</v>
+        <v>1.241940450175888</v>
       </c>
       <c r="G29">
-        <v>-4.290855503391887</v>
+        <v>-4.397445138119801</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.52937544494469</v>
       </c>
       <c r="E30">
-        <v>-27.69393015535575</v>
+        <v>-28.35986942902772</v>
       </c>
       <c r="F30">
-        <v>0.3740996838981798</v>
+        <v>0.9466324412822805</v>
       </c>
       <c r="G30">
-        <v>-4.79363798607762</v>
+        <v>-4.283810662484318</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.34041790673689</v>
       </c>
       <c r="E31">
-        <v>-27.51183115855931</v>
+        <v>-28.06976632714834</v>
       </c>
       <c r="F31">
-        <v>-0.09673440744422562</v>
+        <v>0.9325452252302721</v>
       </c>
       <c r="G31">
-        <v>-4.52204745112689</v>
+        <v>-3.923431296170335</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.0149959210046</v>
       </c>
       <c r="E32">
-        <v>-27.15555346600584</v>
+        <v>-28.4248575595118</v>
       </c>
       <c r="F32">
-        <v>-0.0793337217810192</v>
+        <v>1.164940386616062</v>
       </c>
       <c r="G32">
-        <v>-4.013709873026261</v>
+        <v>-4.073587710195058</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.574244689093312</v>
       </c>
       <c r="E33">
-        <v>-27.42481653050192</v>
+        <v>-27.7527052195013</v>
       </c>
       <c r="F33">
-        <v>-0.0459935905531447</v>
+        <v>1.193933245714045</v>
       </c>
       <c r="G33">
-        <v>-4.263152858319266</v>
+        <v>-4.100022416326139</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.057375263423214</v>
       </c>
       <c r="E34">
-        <v>-27.13703200731447</v>
+        <v>-27.97658391749251</v>
       </c>
       <c r="F34">
-        <v>-0.1014950349081144</v>
+        <v>0.9673084916561562</v>
       </c>
       <c r="G34">
-        <v>-4.198454866845289</v>
+        <v>-4.254336875548186</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.496927508635315</v>
       </c>
       <c r="E35">
-        <v>-26.09521127710983</v>
+        <v>-26.83959277754267</v>
       </c>
       <c r="F35">
-        <v>0.2858081442707945</v>
+        <v>0.754030393192173</v>
       </c>
       <c r="G35">
-        <v>-4.534614281993964</v>
+        <v>-3.570745637689619</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.934551328587337</v>
       </c>
       <c r="E36">
-        <v>-25.17046065695148</v>
+        <v>-27.45868498760529</v>
       </c>
       <c r="F36">
-        <v>-0.02097855172340523</v>
+        <v>1.038183606639682</v>
       </c>
       <c r="G36">
-        <v>-4.540434221052003</v>
+        <v>-3.602732128690057</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.397866699670492</v>
       </c>
       <c r="E37">
-        <v>-26.03587015371332</v>
+        <v>-26.12195644459913</v>
       </c>
       <c r="F37">
-        <v>-0.120192115556702</v>
+        <v>0.8733865387919426</v>
       </c>
       <c r="G37">
-        <v>-4.181345967498335</v>
+        <v>-3.610372867794695</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.917751929474</v>
       </c>
       <c r="E38">
-        <v>-25.92000461775307</v>
+        <v>-26.12717324665597</v>
       </c>
       <c r="F38">
-        <v>0.02629968942397375</v>
+        <v>1.178924885110123</v>
       </c>
       <c r="G38">
-        <v>-4.541712091630162</v>
+        <v>-3.721934941922594</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.507994088805883</v>
       </c>
       <c r="E39">
-        <v>-24.40196956090181</v>
+        <v>-25.29919611604154</v>
       </c>
       <c r="F39">
-        <v>0.05143566989452195</v>
+        <v>0.9077886370302061</v>
       </c>
       <c r="G39">
-        <v>-3.538990884876929</v>
+        <v>-3.428521290776989</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.183306820963315</v>
       </c>
       <c r="E40">
-        <v>-23.51444752556052</v>
+        <v>-24.27326580112981</v>
       </c>
       <c r="F40">
-        <v>-0.2132873577529217</v>
+        <v>1.229398967697503</v>
       </c>
       <c r="G40">
-        <v>-3.544956487938696</v>
+        <v>-3.001954187496357</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.942998563563814</v>
       </c>
       <c r="E41">
-        <v>-23.96997578294009</v>
+        <v>-25.04302034142762</v>
       </c>
       <c r="F41">
-        <v>0.2429409595433228</v>
+        <v>1.016829951730316</v>
       </c>
       <c r="G41">
-        <v>-4.063331640114396</v>
+        <v>-3.03387446758601</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.787458462542321</v>
       </c>
       <c r="E42">
-        <v>-23.73340377230539</v>
+        <v>-23.71899869648698</v>
       </c>
       <c r="F42">
-        <v>-0.004959582888068392</v>
+        <v>1.248055458343353</v>
       </c>
       <c r="G42">
-        <v>-4.069982526102792</v>
+        <v>-3.611180640906277</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.704236411034927</v>
       </c>
       <c r="E43">
-        <v>-22.6074847513043</v>
+        <v>-23.52351805899788</v>
       </c>
       <c r="F43">
-        <v>-0.1508301123166445</v>
+        <v>1.121799012278264</v>
       </c>
       <c r="G43">
-        <v>-4.435079419810236</v>
+        <v>-3.696115997261818</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.683702062366385</v>
       </c>
       <c r="E44">
-        <v>-22.4744110141149</v>
+        <v>-23.43436599120887</v>
       </c>
       <c r="F44">
-        <v>0.1602491835588622</v>
+        <v>1.196088657696129</v>
       </c>
       <c r="G44">
-        <v>-4.962498982399225</v>
+        <v>-2.869942873572379</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.708400794296124</v>
       </c>
       <c r="E45">
-        <v>-21.10292190462586</v>
+        <v>-22.54013728586222</v>
       </c>
       <c r="F45">
-        <v>0.2722577102958001</v>
+        <v>1.10873400160131</v>
       </c>
       <c r="G45">
-        <v>-5.104418759122242</v>
+        <v>-2.93457796468111</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.765705548787398</v>
       </c>
       <c r="E46">
-        <v>-21.44235367387079</v>
+        <v>-22.20721746224032</v>
       </c>
       <c r="F46">
-        <v>0.4294114321179084</v>
+        <v>1.221744852895635</v>
       </c>
       <c r="G46">
-        <v>-5.0978903633188</v>
+        <v>-3.865917188516577</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.840101151182576</v>
       </c>
       <c r="E47">
-        <v>-20.9102443925475</v>
+        <v>-21.37837086461641</v>
       </c>
       <c r="F47">
-        <v>0.2104374793922759</v>
+        <v>1.160334663856497</v>
       </c>
       <c r="G47">
-        <v>-4.829328977536503</v>
+        <v>-4.163084998303716</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.922544989702748</v>
       </c>
       <c r="E48">
-        <v>-20.45289568861684</v>
+        <v>-21.53908187867463</v>
       </c>
       <c r="F48">
-        <v>0.3832713677819759</v>
+        <v>1.562318170147819</v>
       </c>
       <c r="G48">
-        <v>-4.771602994968231</v>
+        <v>-4.265082906368661</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.003982913053899</v>
       </c>
       <c r="E49">
-        <v>-20.85886432645647</v>
+        <v>-20.18724634637888</v>
       </c>
       <c r="F49">
-        <v>0.07253750111343656</v>
+        <v>1.212074491835354</v>
       </c>
       <c r="G49">
-        <v>-5.343837412522334</v>
+        <v>-4.173096088014471</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.080668058107677</v>
       </c>
       <c r="E50">
-        <v>-19.8953092125264</v>
+        <v>-20.58437540295554</v>
       </c>
       <c r="F50">
-        <v>0.2699863268773239</v>
+        <v>1.134428301701345</v>
       </c>
       <c r="G50">
-        <v>-5.315886476534268</v>
+        <v>-4.65600205528242</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.149360427053232</v>
       </c>
       <c r="E51">
-        <v>-19.04177337461267</v>
+        <v>-20.60857103957852</v>
       </c>
       <c r="F51">
-        <v>0.5291733751718585</v>
+        <v>1.672505945333403</v>
       </c>
       <c r="G51">
-        <v>-5.018569692197862</v>
+        <v>-4.326943760315483</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.210806304507051</v>
       </c>
       <c r="E52">
-        <v>-19.21198512713898</v>
+        <v>-19.5033516732665</v>
       </c>
       <c r="F52">
-        <v>0.4048080918873603</v>
+        <v>1.632962998993366</v>
       </c>
       <c r="G52">
-        <v>-5.517366278054312</v>
+        <v>-4.945668168877571</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.267418885256889</v>
       </c>
       <c r="E53">
-        <v>-18.33538124263018</v>
+        <v>-19.71164789219731</v>
       </c>
       <c r="F53">
-        <v>0.5430352752903054</v>
+        <v>1.586060836646858</v>
       </c>
       <c r="G53">
-        <v>-5.28430718263516</v>
+        <v>-4.531247457180525</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.32374062714494</v>
       </c>
       <c r="E54">
-        <v>-17.99108589230101</v>
+        <v>-18.49210719956164</v>
       </c>
       <c r="F54">
-        <v>0.231049745476136</v>
+        <v>1.666228577154989</v>
       </c>
       <c r="G54">
-        <v>-6.109003803014084</v>
+        <v>-4.953904806179278</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.385117399966265</v>
       </c>
       <c r="E55">
-        <v>-17.2806634184517</v>
+        <v>-18.29817077170915</v>
       </c>
       <c r="F55">
-        <v>0.6064517701790243</v>
+        <v>1.564806585825828</v>
       </c>
       <c r="G55">
-        <v>-5.914082192207336</v>
+        <v>-4.911400712000574</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.455819486935658</v>
       </c>
       <c r="E56">
-        <v>-17.35326391374267</v>
+        <v>-18.0832403383571</v>
       </c>
       <c r="F56">
-        <v>0.6494092469534011</v>
+        <v>1.627568670466336</v>
       </c>
       <c r="G56">
-        <v>-6.449748323734649</v>
+        <v>-5.560409991155916</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.540620982801964</v>
       </c>
       <c r="E57">
-        <v>-17.00958896435255</v>
+        <v>-16.89202072216541</v>
       </c>
       <c r="F57">
-        <v>0.6743803823107921</v>
+        <v>1.766277135330307</v>
       </c>
       <c r="G57">
-        <v>-6.386225575927114</v>
+        <v>-5.471819792525019</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.641406694310303</v>
       </c>
       <c r="E58">
-        <v>-16.85047650161904</v>
+        <v>-17.47156576871905</v>
       </c>
       <c r="F58">
-        <v>0.8108961586595534</v>
+        <v>1.788667906227978</v>
       </c>
       <c r="G58">
-        <v>-6.053128415402265</v>
+        <v>-5.553600198981635</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.761150320831655</v>
       </c>
       <c r="E59">
-        <v>-16.23838078389827</v>
+        <v>-16.69718312798539</v>
       </c>
       <c r="F59">
-        <v>0.6388276817500402</v>
+        <v>1.844291120591159</v>
       </c>
       <c r="G59">
-        <v>-6.712095815539734</v>
+        <v>-6.028080827852139</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.898226441396164</v>
       </c>
       <c r="E60">
-        <v>-16.5888529727739</v>
+        <v>-16.75881113075578</v>
       </c>
       <c r="F60">
-        <v>0.9810229423769048</v>
+        <v>1.79069243616042</v>
       </c>
       <c r="G60">
-        <v>-6.543489731224652</v>
+        <v>-6.080930376841064</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.051985117499601</v>
       </c>
       <c r="E61">
-        <v>-16.55467657943801</v>
+        <v>-16.3911896108131</v>
       </c>
       <c r="F61">
-        <v>1.034336668421081</v>
+        <v>1.745874446199355</v>
       </c>
       <c r="G61">
-        <v>-7.035728126367807</v>
+        <v>-6.644170042164967</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.215327727204293</v>
       </c>
       <c r="E62">
-        <v>-14.88838381204964</v>
+        <v>-15.61401743009072</v>
       </c>
       <c r="F62">
-        <v>0.5815005156393004</v>
+        <v>1.986533400795473</v>
       </c>
       <c r="G62">
-        <v>-7.722917927227562</v>
+        <v>-6.132919183989779</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.383641480208365</v>
       </c>
       <c r="E63">
-        <v>-14.58347712863918</v>
+        <v>-16.08919020771557</v>
       </c>
       <c r="F63">
-        <v>0.7102685716696779</v>
+        <v>1.463359743474584</v>
       </c>
       <c r="G63">
-        <v>-7.714320440462075</v>
+        <v>-7.030914593153706</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.546111570676564</v>
       </c>
       <c r="E64">
-        <v>-14.38024827212295</v>
+        <v>-15.53975498483893</v>
       </c>
       <c r="F64">
-        <v>0.6306169040534915</v>
+        <v>1.400625823325772</v>
       </c>
       <c r="G64">
-        <v>-7.740357881128443</v>
+        <v>-7.378915829696354</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.696883305679415</v>
       </c>
       <c r="E65">
-        <v>-14.7428296004951</v>
+        <v>-15.06357235751037</v>
       </c>
       <c r="F65">
-        <v>0.6216407148767561</v>
+        <v>1.770988889117431</v>
       </c>
       <c r="G65">
-        <v>-7.396203498502429</v>
+        <v>-6.863980334335957</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.824184662450834</v>
       </c>
       <c r="E66">
-        <v>-14.29432500630142</v>
+        <v>-15.93475565863199</v>
       </c>
       <c r="F66">
-        <v>0.7754884223942914</v>
+        <v>1.635635312234797</v>
       </c>
       <c r="G66">
-        <v>-7.784119982612069</v>
+        <v>-7.240568131610211</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.923567499471599</v>
       </c>
       <c r="E67">
-        <v>-14.56616930098187</v>
+        <v>-15.40332111993584</v>
       </c>
       <c r="F67">
-        <v>0.381791903600576</v>
+        <v>1.407652035636317</v>
       </c>
       <c r="G67">
-        <v>-7.924844652395408</v>
+        <v>-7.262735544541171</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.984861892405462</v>
       </c>
       <c r="E68">
-        <v>-14.54460470775734</v>
+        <v>-15.96132421563499</v>
       </c>
       <c r="F68">
-        <v>0.3655501039338861</v>
+        <v>1.506946779475088</v>
       </c>
       <c r="G68">
-        <v>-7.61263703422336</v>
+        <v>-7.491365130028778</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.007290014038395</v>
       </c>
       <c r="E69">
-        <v>-14.08035008096498</v>
+        <v>-14.28628243646379</v>
       </c>
       <c r="F69">
-        <v>0.5128363132538466</v>
+        <v>1.831789399748109</v>
       </c>
       <c r="G69">
-        <v>-7.918405641321526</v>
+        <v>-7.764468584290955</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.984168852059243</v>
       </c>
       <c r="E70">
-        <v>-14.80675353958737</v>
+        <v>-14.95491162369632</v>
       </c>
       <c r="F70">
-        <v>0.6717892490748353</v>
+        <v>1.459893854261271</v>
       </c>
       <c r="G70">
-        <v>-7.95717875067747</v>
+        <v>-7.796047878190063</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.91977292718517</v>
       </c>
       <c r="E71">
-        <v>-13.95912736025365</v>
+        <v>-14.59314089217155</v>
       </c>
       <c r="F71">
-        <v>0.4474541025182844</v>
+        <v>1.270343511683077</v>
       </c>
       <c r="G71">
-        <v>-8.368480928476522</v>
+        <v>-7.15326904573963</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.811771367404019</v>
       </c>
       <c r="E72">
-        <v>-14.18781529764101</v>
+        <v>-14.13551595132642</v>
       </c>
       <c r="F72">
-        <v>0.4509597533669319</v>
+        <v>1.102491424853813</v>
       </c>
       <c r="G72">
-        <v>-7.73346532531568</v>
+        <v>-7.573810956138788</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.670577929078519</v>
       </c>
       <c r="E73">
-        <v>-14.35593036670176</v>
+        <v>-15.47636540567956</v>
       </c>
       <c r="F73">
-        <v>0.4413440645552352</v>
+        <v>1.52028349466016</v>
       </c>
       <c r="G73">
-        <v>-8.283721031034561</v>
+        <v>-7.808088332316392</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.498710655169471</v>
       </c>
       <c r="E74">
-        <v>-14.39994713405632</v>
+        <v>-14.9131002231835</v>
       </c>
       <c r="F74">
-        <v>0.3982697879770637</v>
+        <v>1.372307255293668</v>
       </c>
       <c r="G74">
-        <v>-7.493871213002007</v>
+        <v>-7.586199017546741</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.311653416468651</v>
       </c>
       <c r="E75">
-        <v>-14.10831340796235</v>
+        <v>-14.60549456926448</v>
       </c>
       <c r="F75">
-        <v>0.6135177441249041</v>
+        <v>1.132831209348748</v>
       </c>
       <c r="G75">
-        <v>-7.374721368498097</v>
+        <v>-7.525725282180874</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.114087580851608</v>
       </c>
       <c r="E76">
-        <v>-14.27298683677727</v>
+        <v>-14.57570173876801</v>
       </c>
       <c r="F76">
-        <v>0.2430486473056868</v>
+        <v>0.9126113920493047</v>
       </c>
       <c r="G76">
-        <v>-7.436615327900311</v>
+        <v>-7.066536063156264</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.923097310574781</v>
       </c>
       <c r="E77">
-        <v>-14.87182771107759</v>
+        <v>-15.32877338082157</v>
       </c>
       <c r="F77">
-        <v>0.2877639197088041</v>
+        <v>0.7629403129766845</v>
       </c>
       <c r="G77">
-        <v>-6.542109233734776</v>
+        <v>-6.801811599653983</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.742467237169312</v>
       </c>
       <c r="E78">
-        <v>-15.24817560043305</v>
+        <v>-15.80751459596446</v>
       </c>
       <c r="F78">
-        <v>0.1927095886049636</v>
+        <v>0.9241306691526348</v>
       </c>
       <c r="G78">
-        <v>-7.146935972123004</v>
+        <v>-6.656726941395423</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.588710452971995</v>
       </c>
       <c r="E79">
-        <v>-15.06396180627503</v>
+        <v>-15.93141364481433</v>
       </c>
       <c r="F79">
-        <v>0.08962340716357915</v>
+        <v>0.6235832364363209</v>
       </c>
       <c r="G79">
-        <v>-6.737563842373347</v>
+        <v>-6.700035498140169</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.461975234297243</v>
       </c>
       <c r="E80">
-        <v>-15.05720079458158</v>
+        <v>-16.16930796985927</v>
       </c>
       <c r="F80">
-        <v>-0.3552264554878113</v>
+        <v>0.9521526816545364</v>
       </c>
       <c r="G80">
-        <v>-7.06060356554989</v>
+        <v>-6.390992761503664</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.375926677775674</v>
       </c>
       <c r="E81">
-        <v>-15.91605306098031</v>
+        <v>-16.49333387053011</v>
       </c>
       <c r="F81">
-        <v>-0.3854635224247989</v>
+        <v>0.9832098323202955</v>
       </c>
       <c r="G81">
-        <v>-7.264619244953016</v>
+        <v>-6.405330734234248</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.325332332171701</v>
       </c>
       <c r="E82">
-        <v>-17.6178354791668</v>
+        <v>-18.08792278048103</v>
       </c>
       <c r="F82">
-        <v>-0.03220210166393574</v>
+        <v>0.4091363115669877</v>
       </c>
       <c r="G82">
-        <v>-6.710374331859312</v>
+        <v>-6.4276239478957</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.318663079348645</v>
       </c>
       <c r="E83">
-        <v>-16.92452610859247</v>
+        <v>-19.00927704513363</v>
       </c>
       <c r="F83">
-        <v>-0.6289173886379624</v>
+        <v>0.3843888354083524</v>
       </c>
       <c r="G83">
-        <v>-7.099310463995049</v>
+        <v>-6.277629750602401</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.344361371284826</v>
       </c>
       <c r="E84">
-        <v>-17.94603663287271</v>
+        <v>-18.95291112916016</v>
       </c>
       <c r="F84">
-        <v>-0.2571908301012955</v>
+        <v>0.3040082044777024</v>
       </c>
       <c r="G84">
-        <v>-6.070316767842161</v>
+        <v>-5.879841219694653</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.408783626570848</v>
       </c>
       <c r="E85">
-        <v>-19.27395276545994</v>
+        <v>-20.60662832422923</v>
       </c>
       <c r="F85">
-        <v>-0.7071103012578189</v>
+        <v>0.2683420175827669</v>
       </c>
       <c r="G85">
-        <v>-6.673845772378995</v>
+        <v>-5.966332532453652</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.499545731536238</v>
       </c>
       <c r="E86">
-        <v>-20.5934414079189</v>
+        <v>-21.70056726178816</v>
       </c>
       <c r="F86">
-        <v>-0.7400867791958644</v>
+        <v>-0.1550282783140324</v>
       </c>
       <c r="G86">
-        <v>-6.125122849244796</v>
+        <v>-5.302167575819528</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.626009510943724</v>
       </c>
       <c r="E87">
-        <v>-21.57226653620284</v>
+        <v>-22.67163964257096</v>
       </c>
       <c r="F87">
-        <v>-1.06425925024002</v>
+        <v>0.1227084012313914</v>
       </c>
       <c r="G87">
-        <v>-5.800298742022584</v>
+        <v>-5.914025912933168</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.777218799727974</v>
       </c>
       <c r="E88">
-        <v>-23.07304357861086</v>
+        <v>-23.39013185710195</v>
       </c>
       <c r="F88">
-        <v>-0.9295012695199995</v>
+        <v>-0.1363659890963624</v>
       </c>
       <c r="G88">
-        <v>-5.314886691781408</v>
+        <v>-5.465079521807063</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.96594910429285</v>
       </c>
       <c r="E89">
-        <v>-25.03306675555876</v>
+        <v>-25.38242493982851</v>
       </c>
       <c r="F89">
-        <v>-1.126575673217821</v>
+        <v>-0.2582801332359768</v>
       </c>
       <c r="G89">
-        <v>-5.088365923802316</v>
+        <v>-5.048016994769679</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.181889095006126</v>
       </c>
       <c r="E90">
-        <v>-26.41909679508643</v>
+        <v>-27.13765693672753</v>
       </c>
       <c r="F90">
-        <v>-1.383912977101905</v>
+        <v>-0.3997147552225616</v>
       </c>
       <c r="G90">
-        <v>-5.212600766254546</v>
+        <v>-4.72827457495025</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.440511228688387</v>
       </c>
       <c r="E91">
-        <v>-28.0709210880203</v>
+        <v>-28.32631343663088</v>
       </c>
       <c r="F91">
-        <v>-1.724310680464694</v>
+        <v>-0.9915807794206</v>
       </c>
       <c r="G91">
-        <v>-5.847646164325242</v>
+        <v>-5.156867732100915</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.730769826804069</v>
       </c>
       <c r="E92">
-        <v>-29.54556883540407</v>
+        <v>-30.16199830275018</v>
       </c>
       <c r="F92">
-        <v>-1.805439327160072</v>
+        <v>-0.9160858594316614</v>
       </c>
       <c r="G92">
-        <v>-5.326132614978312</v>
+        <v>-5.482430090978383</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.068732090218855</v>
       </c>
       <c r="E93">
-        <v>-31.06308311774444</v>
+        <v>-31.81350786674052</v>
       </c>
       <c r="F93">
-        <v>-1.730905313358381</v>
+        <v>-0.8727266244669268</v>
       </c>
       <c r="G93">
-        <v>-5.158407135776677</v>
+        <v>-4.833569786372309</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.440722747696935</v>
       </c>
       <c r="E94">
-        <v>-33.18229347724697</v>
+        <v>-33.31984813946696</v>
       </c>
       <c r="F94">
-        <v>-2.223140276552112</v>
+        <v>-1.442213474910934</v>
       </c>
       <c r="G94">
-        <v>-5.599815414709861</v>
+        <v>-4.797402076355771</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.859520258523796</v>
       </c>
       <c r="E95">
-        <v>-35.6830685281618</v>
+        <v>-36.32035388255024</v>
       </c>
       <c r="F95">
-        <v>-2.490679753369074</v>
+        <v>-1.756737950814684</v>
       </c>
       <c r="G95">
-        <v>-5.501998725661015</v>
+        <v>-5.603923801724097</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.310899561331405</v>
       </c>
       <c r="E96">
-        <v>-37.70894930260325</v>
+        <v>-38.92896322077272</v>
       </c>
       <c r="F96">
-        <v>-2.71275594201819</v>
+        <v>-1.627181289016841</v>
       </c>
       <c r="G96">
-        <v>-5.429964565272013</v>
+        <v>-5.138384956355164</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.799177133440386</v>
       </c>
       <c r="E97">
-        <v>-39.64140765826646</v>
+        <v>-41.25301910201222</v>
       </c>
       <c r="F97">
-        <v>-3.048380592406049</v>
+        <v>-2.106971688718315</v>
       </c>
       <c r="G97">
-        <v>-5.308139799972373</v>
+        <v>-4.787632656469382</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.3134101822797</v>
       </c>
       <c r="E98">
-        <v>-42.79605359962282</v>
+        <v>-43.73587271704169</v>
       </c>
       <c r="F98">
-        <v>-3.11746394869732</v>
+        <v>-1.979623454416336</v>
       </c>
       <c r="G98">
-        <v>-5.755450781602078</v>
+        <v>-5.353871676051865</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.84365725952633</v>
       </c>
       <c r="E99">
-        <v>-45.25070387853252</v>
+        <v>-45.39927178953917</v>
       </c>
       <c r="F99">
-        <v>-3.772922081673471</v>
+        <v>-2.587732106648466</v>
       </c>
       <c r="G99">
-        <v>-6.288640625066017</v>
+        <v>-5.688263259882569</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.39210331244142</v>
       </c>
       <c r="E100">
-        <v>-47.81507455417407</v>
+        <v>-48.36318746264047</v>
       </c>
       <c r="F100">
-        <v>-3.876539246620049</v>
+        <v>-2.71045390900581</v>
       </c>
       <c r="G100">
-        <v>-6.888455197507788</v>
+        <v>-5.579078157451867</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.91991780849832</v>
       </c>
       <c r="E101">
-        <v>-50.29576695498338</v>
+        <v>-50.43655268340785</v>
       </c>
       <c r="F101">
-        <v>-4.061501262154137</v>
+        <v>-3.129645919722889</v>
       </c>
       <c r="G101">
-        <v>-6.535531179748244</v>
+        <v>-5.891113627255872</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.47265587279618</v>
       </c>
       <c r="E102">
-        <v>-52.24760265092542</v>
+        <v>-53.25782935009704</v>
       </c>
       <c r="F102">
-        <v>-4.465612015935847</v>
+        <v>-3.59782757864153</v>
       </c>
       <c r="G102">
-        <v>-6.810673930062612</v>
+        <v>-6.537689655439849</v>
       </c>
     </row>
   </sheetData>
